--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260901.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260901.xlsx
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2,565,000</t>
+          <t>13,112,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>13,112,000</t>
+          <t>2,565,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>遠百</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>24,799,000</t>
+          <t>35,227,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>遠百</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>35,227,000</t>
+          <t>24,799,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
